--- a/research/traditional_assets/database/data/vietnam/vietnam_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.154</v>
+        <v>0.123</v>
       </c>
       <c r="E2">
-        <v>0.0766</v>
+        <v>0.0593</v>
       </c>
       <c r="G2">
-        <v>0.07993514788248009</v>
+        <v>0.07185685733320643</v>
       </c>
       <c r="H2">
-        <v>0.07993514788248009</v>
+        <v>0.07185685733320643</v>
       </c>
       <c r="I2">
-        <v>0.07001080868625331</v>
+        <v>0.07542590653849814</v>
       </c>
       <c r="J2">
-        <v>0.05963371253710509</v>
+        <v>0.06160186579028465</v>
       </c>
       <c r="K2">
-        <v>81.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="L2">
-        <v>0.04023779109757296</v>
+        <v>0.03445322166174931</v>
       </c>
       <c r="M2">
-        <v>26.7</v>
+        <v>28.8</v>
       </c>
       <c r="N2">
-        <v>0.01459734295555191</v>
+        <v>0.01982242411728267</v>
       </c>
       <c r="O2">
-        <v>0.326007326007326</v>
+        <v>0.3977900552486188</v>
       </c>
       <c r="P2">
-        <v>26.7</v>
+        <v>28.8</v>
       </c>
       <c r="Q2">
-        <v>0.01459734295555191</v>
+        <v>0.01982242411728267</v>
       </c>
       <c r="R2">
-        <v>0.326007326007326</v>
+        <v>0.3977900552486188</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>696.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="V2">
-        <v>0.3806790224700672</v>
+        <v>0.06497350127331544</v>
       </c>
       <c r="W2">
-        <v>0.09422457432121491</v>
+        <v>0.07739176910742919</v>
       </c>
       <c r="X2">
-        <v>0.09408687972236138</v>
+        <v>0.1305237652861561</v>
       </c>
       <c r="Y2">
-        <v>0.00013769459885353</v>
+        <v>-0.05313199617872687</v>
       </c>
       <c r="Z2">
-        <v>2.669027012850774</v>
+        <v>6.029842180774749</v>
       </c>
       <c r="AA2">
-        <v>0.1591639896381113</v>
+        <v>0.3714495287566834</v>
       </c>
       <c r="AB2">
-        <v>0.09121635837648948</v>
+        <v>0.1283185831659477</v>
       </c>
       <c r="AC2">
-        <v>0.06794763126162184</v>
+        <v>0.2431309455907358</v>
       </c>
       <c r="AD2">
-        <v>109.3</v>
+        <v>52.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>109.3</v>
+        <v>52.5</v>
       </c>
       <c r="AG2">
-        <v>-587</v>
+        <v>-41.90000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.05638671068922823</v>
+        <v>0.03487445197289757</v>
       </c>
       <c r="AI2">
-        <v>0.101082030888745</v>
+        <v>0.05129457743038593</v>
       </c>
       <c r="AJ2">
-        <v>-0.4725867482489333</v>
+        <v>-0.02969525159461375</v>
       </c>
       <c r="AK2">
-        <v>-1.524675324675325</v>
+        <v>-0.04509740609191691</v>
       </c>
       <c r="AL2">
-        <v>30.1</v>
+        <v>38.3</v>
       </c>
       <c r="AM2">
-        <v>30.1</v>
+        <v>38.3</v>
       </c>
       <c r="AN2">
-        <v>0.7315930388219545</v>
+        <v>0.3185679611650485</v>
       </c>
       <c r="AO2">
-        <v>4.73421926910299</v>
+        <v>4.138381201044386</v>
       </c>
       <c r="AP2">
-        <v>-3.92904953145917</v>
+        <v>-0.254247572815534</v>
       </c>
       <c r="AQ2">
-        <v>4.73421926910299</v>
+        <v>4.138381201044386</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.154</v>
+        <v>0.123</v>
       </c>
       <c r="E3">
-        <v>0.0766</v>
+        <v>0.0593</v>
       </c>
       <c r="G3">
-        <v>0.07993514788248009</v>
+        <v>0.07185685733320643</v>
       </c>
       <c r="H3">
-        <v>0.07993514788248009</v>
+        <v>0.07185685733320643</v>
       </c>
       <c r="I3">
-        <v>0.07001080868625331</v>
+        <v>0.07542590653849814</v>
       </c>
       <c r="J3">
-        <v>0.05963371253710509</v>
+        <v>0.06160186579028465</v>
       </c>
       <c r="K3">
-        <v>81.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="L3">
-        <v>0.04023779109757296</v>
+        <v>0.03445322166174931</v>
       </c>
       <c r="M3">
-        <v>26.7</v>
+        <v>28.8</v>
       </c>
       <c r="N3">
-        <v>0.01459734295555191</v>
+        <v>0.01982242411728267</v>
       </c>
       <c r="O3">
-        <v>0.326007326007326</v>
+        <v>0.3977900552486188</v>
       </c>
       <c r="P3">
-        <v>26.7</v>
+        <v>28.8</v>
       </c>
       <c r="Q3">
-        <v>0.01459734295555191</v>
+        <v>0.01982242411728267</v>
       </c>
       <c r="R3">
-        <v>0.326007326007326</v>
+        <v>0.3977900552486188</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>696.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="V3">
-        <v>0.3806790224700672</v>
+        <v>0.06497350127331544</v>
       </c>
       <c r="W3">
-        <v>0.09422457432121491</v>
+        <v>0.07739176910742919</v>
       </c>
       <c r="X3">
-        <v>0.09408687972236138</v>
+        <v>0.1305237652861561</v>
       </c>
       <c r="Y3">
-        <v>0.00013769459885353</v>
+        <v>-0.05313199617872687</v>
       </c>
       <c r="Z3">
-        <v>2.669027012850774</v>
+        <v>6.029842180774749</v>
       </c>
       <c r="AA3">
-        <v>0.1591639896381113</v>
+        <v>0.3714495287566834</v>
       </c>
       <c r="AB3">
-        <v>0.09121635837648948</v>
+        <v>0.1283185831659477</v>
       </c>
       <c r="AC3">
-        <v>0.06794763126162184</v>
+        <v>0.2431309455907358</v>
       </c>
       <c r="AD3">
-        <v>109.3</v>
+        <v>52.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>109.3</v>
+        <v>52.5</v>
       </c>
       <c r="AG3">
-        <v>-587</v>
+        <v>-41.90000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.05638671068922823</v>
+        <v>0.03487445197289757</v>
       </c>
       <c r="AI3">
-        <v>0.101082030888745</v>
+        <v>0.05129457743038593</v>
       </c>
       <c r="AJ3">
-        <v>-0.4725867482489333</v>
+        <v>-0.02969525159461375</v>
       </c>
       <c r="AK3">
-        <v>-1.524675324675325</v>
+        <v>-0.04509740609191691</v>
       </c>
       <c r="AL3">
-        <v>30.1</v>
+        <v>38.3</v>
       </c>
       <c r="AM3">
-        <v>30.1</v>
+        <v>38.3</v>
       </c>
       <c r="AN3">
-        <v>0.7315930388219545</v>
+        <v>0.3185679611650485</v>
       </c>
       <c r="AO3">
-        <v>4.73421926910299</v>
+        <v>4.138381201044386</v>
       </c>
       <c r="AP3">
-        <v>-3.92904953145917</v>
+        <v>-0.254247572815534</v>
       </c>
       <c r="AQ3">
-        <v>4.73421926910299</v>
+        <v>4.138381201044386</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/vietnam/vietnam_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.123</v>
+        <v>0.0824</v>
       </c>
       <c r="E2">
-        <v>0.0593</v>
+        <v>0.0527</v>
       </c>
       <c r="G2">
-        <v>0.07185685733320643</v>
+        <v>0.07387685698943976</v>
       </c>
       <c r="H2">
-        <v>0.07185685733320643</v>
+        <v>0.07387685698943976</v>
       </c>
       <c r="I2">
-        <v>0.07542590653849814</v>
+        <v>0.08591372829783425</v>
       </c>
       <c r="J2">
-        <v>0.06160186579028465</v>
+        <v>0.07080279599766208</v>
       </c>
       <c r="K2">
-        <v>72.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="L2">
-        <v>0.03445322166174931</v>
+        <v>0.03190442097726866</v>
       </c>
       <c r="M2">
-        <v>28.8</v>
+        <v>96.2</v>
       </c>
       <c r="N2">
-        <v>0.01982242411728267</v>
+        <v>0.08001996340043253</v>
       </c>
       <c r="O2">
-        <v>0.3977900552486188</v>
+        <v>1.349228611500701</v>
       </c>
       <c r="P2">
-        <v>28.8</v>
+        <v>96.2</v>
       </c>
       <c r="Q2">
-        <v>0.01982242411728267</v>
+        <v>0.08001996340043253</v>
       </c>
       <c r="R2">
-        <v>0.3977900552486188</v>
+        <v>1.349228611500701</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>94.40000000000001</v>
+        <v>299.2</v>
       </c>
       <c r="V2">
-        <v>0.06497350127331544</v>
+        <v>0.2488770587256696</v>
       </c>
       <c r="W2">
-        <v>0.07739176910742919</v>
+        <v>0.07577850993729408</v>
       </c>
       <c r="X2">
-        <v>0.1305237652861561</v>
+        <v>0.1135205478038425</v>
       </c>
       <c r="Y2">
-        <v>-0.05313199617872687</v>
+        <v>-0.03774203786654844</v>
       </c>
       <c r="Z2">
-        <v>6.029842180774749</v>
+        <v>2.542145375952679</v>
       </c>
       <c r="AA2">
-        <v>0.3714495287566834</v>
+        <v>0.1799910004499775</v>
       </c>
       <c r="AB2">
-        <v>0.1283185831659477</v>
+        <v>0.1095875675295585</v>
       </c>
       <c r="AC2">
-        <v>0.2431309455907358</v>
+        <v>0.07040343292041897</v>
       </c>
       <c r="AD2">
-        <v>52.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>52.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AG2">
-        <v>-41.90000000000001</v>
+        <v>-199.3</v>
       </c>
       <c r="AH2">
-        <v>0.03487445197289757</v>
+        <v>0.07672221795561017</v>
       </c>
       <c r="AI2">
-        <v>0.05129457743038593</v>
+        <v>0.09612239007023959</v>
       </c>
       <c r="AJ2">
-        <v>-0.02969525159461375</v>
+        <v>-0.1987237012663276</v>
       </c>
       <c r="AK2">
-        <v>-0.04509740609191691</v>
+        <v>-0.2692879340629644</v>
       </c>
       <c r="AL2">
-        <v>38.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AM2">
-        <v>38.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AN2">
-        <v>0.3185679611650485</v>
+        <v>0.5078800203355364</v>
       </c>
       <c r="AO2">
-        <v>4.138381201044386</v>
+        <v>2.382133995037221</v>
       </c>
       <c r="AP2">
-        <v>-0.254247572815534</v>
+        <v>-1.013218098627351</v>
       </c>
       <c r="AQ2">
-        <v>4.138381201044386</v>
+        <v>2.382133995037221</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.123</v>
+        <v>0.0824</v>
       </c>
       <c r="E3">
-        <v>0.0593</v>
+        <v>0.0527</v>
       </c>
       <c r="G3">
-        <v>0.07185685733320643</v>
+        <v>0.07387685698943976</v>
       </c>
       <c r="H3">
-        <v>0.07185685733320643</v>
+        <v>0.07387685698943976</v>
       </c>
       <c r="I3">
-        <v>0.07542590653849814</v>
+        <v>0.08591372829783425</v>
       </c>
       <c r="J3">
-        <v>0.06160186579028465</v>
+        <v>0.07080279599766208</v>
       </c>
       <c r="K3">
-        <v>72.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="L3">
-        <v>0.03445322166174931</v>
+        <v>0.03190442097726866</v>
       </c>
       <c r="M3">
-        <v>28.8</v>
+        <v>96.2</v>
       </c>
       <c r="N3">
-        <v>0.01982242411728267</v>
+        <v>0.08001996340043253</v>
       </c>
       <c r="O3">
-        <v>0.3977900552486188</v>
+        <v>1.349228611500701</v>
       </c>
       <c r="P3">
-        <v>28.8</v>
+        <v>96.2</v>
       </c>
       <c r="Q3">
-        <v>0.01982242411728267</v>
+        <v>0.08001996340043253</v>
       </c>
       <c r="R3">
-        <v>0.3977900552486188</v>
+        <v>1.349228611500701</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>94.40000000000001</v>
+        <v>299.2</v>
       </c>
       <c r="V3">
-        <v>0.06497350127331544</v>
+        <v>0.2488770587256696</v>
       </c>
       <c r="W3">
-        <v>0.07739176910742919</v>
+        <v>0.07577850993729408</v>
       </c>
       <c r="X3">
-        <v>0.1305237652861561</v>
+        <v>0.1135205478038425</v>
       </c>
       <c r="Y3">
-        <v>-0.05313199617872687</v>
+        <v>-0.03774203786654844</v>
       </c>
       <c r="Z3">
-        <v>6.029842180774749</v>
+        <v>2.542145375952679</v>
       </c>
       <c r="AA3">
-        <v>0.3714495287566834</v>
+        <v>0.1799910004499775</v>
       </c>
       <c r="AB3">
-        <v>0.1283185831659477</v>
+        <v>0.1095875675295585</v>
       </c>
       <c r="AC3">
-        <v>0.2431309455907358</v>
+        <v>0.07040343292041897</v>
       </c>
       <c r="AD3">
-        <v>52.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>52.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AG3">
-        <v>-41.90000000000001</v>
+        <v>-199.3</v>
       </c>
       <c r="AH3">
-        <v>0.03487445197289757</v>
+        <v>0.07672221795561017</v>
       </c>
       <c r="AI3">
-        <v>0.05129457743038593</v>
+        <v>0.09612239007023959</v>
       </c>
       <c r="AJ3">
-        <v>-0.02969525159461375</v>
+        <v>-0.1987237012663276</v>
       </c>
       <c r="AK3">
-        <v>-0.04509740609191691</v>
+        <v>-0.2692879340629644</v>
       </c>
       <c r="AL3">
-        <v>38.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AM3">
-        <v>38.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AN3">
-        <v>0.3185679611650485</v>
+        <v>0.5078800203355364</v>
       </c>
       <c r="AO3">
-        <v>4.138381201044386</v>
+        <v>2.382133995037221</v>
       </c>
       <c r="AP3">
-        <v>-0.254247572815534</v>
+        <v>-1.013218098627351</v>
       </c>
       <c r="AQ3">
-        <v>4.138381201044386</v>
+        <v>2.382133995037221</v>
       </c>
     </row>
   </sheetData>
